--- a/Recruiters/Tier_A_Verified_Recruiters.xlsx
+++ b/Recruiters/Tier_A_Verified_Recruiters.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tier A Verified" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Recruiters" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,7 +44,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +59,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -426,19 +435,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,519 +457,576 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AUM_Bucket</t>
+          <t>Firm</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Firm</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>AUM (approx.)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>AUM_Approx</t>
+          <t>Named Contact</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Named_Contact</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>USC Connection</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>USC_Connection</t>
+          <t>Official Source URL</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Official_Source_URL</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>$1-10B</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Silver Lake</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>PE / Alternatives</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>100B+</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Tezira Nabongo</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Talent Partner</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>J.D. and M.A. University of Southern California</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.silverlake.com/people/tezira-nabongo/</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Direct talent/recruiting role</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Apollo Global Management</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PE / Alternatives</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>750B+</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Matthew Breitfelder</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Partner Global Head of Human Capital</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>B.A. Economics University of Southern California</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apollo.com/aboutus/leadership-and-people/matthew-breitfelder</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Firmwide HR leader not campus-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Andreessen Horowitz (a16z)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40B+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Erika Louie</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Partner HR team</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>B.S. Public Policy USC Dean's Scholar</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://a16z.com/author/erika-louie/</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>VC/portfolio talent acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>PIMCO</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1.9T+</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Kimberley Stafford</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>MD Global Head of Product Strategy (formerly Global Head of HR and Talent Management)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>MBA Marshall School of Business USC</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pimco.com/mea/en/experts/kimberley-stafford</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Former firmwide HR/talent head</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FS Investments</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Alternatives / Credit</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82B</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Scott Stimpfel</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Head of Human Resources</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>B.S. Business Administration University of Southern California</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://fsinvestments.com/fs-investments-hires-scott-stimpfel-as-head-of-human-resources/</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Oversees early talent programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Gryphon Investors</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>~$7B</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Barry Becker</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Managing Director, Human Resources team</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>MBA specializing in Human Resources, University of Southern California</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>https://www.gryphon-inv.com/team/barry-becker/</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Operations Resources Group; portfolio company HR/talent initiatives</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>$1-10B AUM focus; portfolio HR/talent initiatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>$1-10B</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>JMI Equity</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Growth Equity / Software PE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>~$6B</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Haley Donzella</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Master's in Human Resource Management, University of Southern California</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>https://www.jmi.com/team/donzella-haley/</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Internal talent, professional development, performance management</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>$1-10B AUM focus; internal talent programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>$1-10B</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Silver Lake</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PE / Alternatives</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>~$100B+</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tezira Nabongo</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Talent Partner</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>J.D. and M.A., University of Southern California</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://www.silverlake.com/people/tezira-nabongo/</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above $10B but core Tier A match</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Chandler Asset Management</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management (Public Sector)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45B</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Adriana Haefner, SHRM-SCP</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Director of Human Resources</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Bachelor of Arts, University of Southern California</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chandlerasset.com/team-members/adriana-haefner-shrm-scp-cpsp/</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Oversees recruiting; municipal/public agency AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>$1-10B</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Apollo Global Management</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PE / Alternatives</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>~$750B+</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Matthew Breitfelder</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Partner, Global Head of Human Capital</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>B.A. Economics, University of Southern California</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>https://www.apollo.com/aboutus/leadership-and-people/matthew-breitfelder</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Firmwide HR leader</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Cerity Partners</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>100B+ RAUM</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Madlene Asikian</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Associate Human Capital team</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>B.A. Psychology and M.A. HR Management USC</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://ceritypartners.com/team/madlene-asikian/</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>HR operations not dedicated campus recruiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$1-10B</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Andreessen Horowitz (a16z)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Venture Capital</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>~$40B+</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Erika Louie</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Partner, HR team</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>B.S. Public Policy, USC (Dean's Scholar)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>https://a16z.com/author/erika-louie/</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>VC/portfolio talent acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pathway Capital Management</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Private Markets / FoF</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>125B+ committed</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Jodi M. Field</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources Manager</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Master's in occupational social work University of Southern California</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://pathwaycapital.com/team/jodi-field/</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Primary responsibility talent acquisition; PE/credit/infrastructure FoF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>$1-10B</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PIMCO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Causeway Capital Management</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Asset Management</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>~$1.9T+</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Kimberley Stafford</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MD; formerly Global Head of HR &amp; Talent Management</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>MBA, Marshall School of Business, USC</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://www.pimco.com/mea/en/experts/kimberley-stafford</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Now Global Head of Product Strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>$1-10B</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FS Investments</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Alternatives / Credit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>~$82B</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dr. Scott Stimpfel</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Head of Human Resources</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>B.S. Business Administration, USC</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://fsinvestments.com/fs-investments-hires-scott-stimpfel-as-head-of-human-resources/</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Oversees early talent programs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>$1-10B</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Cerity Partners</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Wealth Management</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>~$100B+ RAUM</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Madlene Asikian</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Senior Associate, Human Capital team</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>B.A. Psychology + M.A. HR Management, USC</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>https://ceritypartners.com/team/madlene-asikian/</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>HR operations support</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>$10B+</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Chandler Asset Management</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Asset Management (Public Sector)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>~$45B</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Adriana Haefner, SHRM-SCP</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79B</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Jaime Rochon</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Director of Human Resources</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Bachelor of Arts, University of Southern California</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>https://www.chandlerasset.com/team-members/adriana-haefner-shrm-scp-cpsp/</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Oversees recruiting, training, culture; municipal/public agency AM</t>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>B.A. Phi Beta Kappa University of Southern California</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.causewaycap.com/person/jaime-rochon/</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Oversees employee relations benefits and recruiting</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>